--- a/english.xlsx
+++ b/english.xlsx
@@ -5,15 +5,17 @@
   <sheets>
     <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'시트1'!$A$1:$C$99</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Day</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+  <si>
+    <t>Week</t>
   </si>
   <si>
     <t>영어</t>
@@ -22,22 +24,592 @@
     <t>한국어</t>
   </si>
   <si>
-    <t>I don’t get you.</t>
-  </si>
-  <si>
-    <t>난 네가 이해 안 돼.</t>
-  </si>
-  <si>
-    <t>I don’t get why she said that.</t>
-  </si>
-  <si>
-    <t>난 걔가 왜 그런 말을 했는지 이해 안 돼.</t>
-  </si>
-  <si>
-    <t>I don’t get this question. What’s the answer?</t>
-  </si>
-  <si>
-    <t>난 이 문제가 이해 안 돼. 답이 뭐야?</t>
+    <t>I don't get you.</t>
+  </si>
+  <si>
+    <t>넌 날 이해 못 해.</t>
+  </si>
+  <si>
+    <t>I don't get why she said that.</t>
+  </si>
+  <si>
+    <t>걔가 왜 그렇게 말했는지 모르겠어.</t>
+  </si>
+  <si>
+    <t>I don't get what you're saying.</t>
+  </si>
+  <si>
+    <t>네가 무슨 말을 하는지 모르겠어.</t>
+  </si>
+  <si>
+    <t>I don't get what this question is. What's the answer?</t>
+  </si>
+  <si>
+    <t>이 질문이 뭔지 모르겠어. 답이 뭐야?</t>
+  </si>
+  <si>
+    <t>I don't get what just happened here.</t>
+  </si>
+  <si>
+    <t>방금 무슨 일이 있었는지 모르겠어.</t>
+  </si>
+  <si>
+    <t>I'll go get us something to eat.</t>
+  </si>
+  <si>
+    <t>내가 우리 먹을 것 좀 가지고 올게.</t>
+  </si>
+  <si>
+    <t>I'll go get my stuff.</t>
+  </si>
+  <si>
+    <t>내 물건 가지고 올게. (내 물건 좀 챙겨올게)</t>
+  </si>
+  <si>
+    <t>I'll go get it for you.</t>
+  </si>
+  <si>
+    <t>내가 네 대신 그거 가지고 와 줄게.</t>
+  </si>
+  <si>
+    <t>I'll go get a pen and paper.</t>
+  </si>
+  <si>
+    <t>내가 필기도구 가지고 올게.</t>
+  </si>
+  <si>
+    <t>I'll go get the car keys.</t>
+  </si>
+  <si>
+    <t>내가 차 키 좀 가지고 올게.</t>
+  </si>
+  <si>
+    <t>I got you something for your birthday.</t>
+  </si>
+  <si>
+    <t>너 생일 선물로 주려고 뭐 좀 샀어.</t>
+  </si>
+  <si>
+    <t>I got you some ice cream, your favorite.</t>
+  </si>
+  <si>
+    <t>너 주려고 아이스크림 좀 갖고 왔어, 네가 제일 좋아하는 걸로 말이야.</t>
+  </si>
+  <si>
+    <t>I got you this as a thank-you.</t>
+  </si>
+  <si>
+    <t>감사의 표시로 너 주려고 이걸 샀어.</t>
+  </si>
+  <si>
+    <t>I got you something. You're gonna love it.</t>
+  </si>
+  <si>
+    <t>너 주려고 뭐 하나 샀어. 너 정말 맘에 들어할 거야.</t>
+  </si>
+  <si>
+    <t>I got you a little something.</t>
+  </si>
+  <si>
+    <t>너 주려고 조그만 거 하나 샀어.</t>
+  </si>
+  <si>
+    <t>I've got a problem with my schedule.</t>
+  </si>
+  <si>
+    <t>나 스케줄에 문제가 있어.</t>
+  </si>
+  <si>
+    <t>I've got a problem with your attitude.</t>
+  </si>
+  <si>
+    <t>난 네 태도가 마음에 안 들어.</t>
+  </si>
+  <si>
+    <t>I've got a problem with my computer.</t>
+  </si>
+  <si>
+    <t>내 컴퓨터에 문제가 생겼어.</t>
+  </si>
+  <si>
+    <t>I've got a problem with my girlfriend.</t>
+  </si>
+  <si>
+    <t>나 여자 친구하고 문제가 있어.</t>
+  </si>
+  <si>
+    <t>I've got a problem with the way you avoid responsibility.</t>
+  </si>
+  <si>
+    <t>난 네가 책임 회피하는 게 마음에 안 들어.</t>
+  </si>
+  <si>
+    <t>How did you get her to tell you the truth?</t>
+  </si>
+  <si>
+    <t>너 어떻게 걔가 진실을 말하게 했어?</t>
+  </si>
+  <si>
+    <t>How did you get him to listen to you?</t>
+  </si>
+  <si>
+    <t>너 어떻게 걔가 네 말을 듣게 한 거니?</t>
+  </si>
+  <si>
+    <t>How did you get her to calm down?</t>
+  </si>
+  <si>
+    <t>너 어떻게 걔가 진정하게 했어? (걔를 진정시켰어?)</t>
+  </si>
+  <si>
+    <t>How did you get the manager to sign off on that?</t>
+  </si>
+  <si>
+    <t>너 어떻게 매니저가 그걸 승낙하게 한 거야? (너 어떻게 매니저한테 허락을 받은 거야?)</t>
+  </si>
+  <si>
+    <t>Are you saying you're not even gonna help?</t>
+  </si>
+  <si>
+    <t>너 지금 도와주지도 않을 거라고 말하는 거야?</t>
+  </si>
+  <si>
+    <t>Are you saying that this plan won't work?</t>
+  </si>
+  <si>
+    <t>너 지금 이 계획이 실패할 거라고 말하는 거야?</t>
+  </si>
+  <si>
+    <t>Are you saying you don't trust me?</t>
+  </si>
+  <si>
+    <t>너 지금 날 안 믿는다고 말하는 거야?</t>
+  </si>
+  <si>
+    <t>Are you saying I have no life?</t>
+  </si>
+  <si>
+    <t>너 지금 내가 할 일 없이 빈둥대기만 한다고 말하는 거야?</t>
+  </si>
+  <si>
+    <t>Are you saying you're going to give up without even trying?</t>
+  </si>
+  <si>
+    <t>너 지금 해 보지도 않고 포기할 거라고 말하는 거야?</t>
+  </si>
+  <si>
+    <t>All I'm saying is it's worth a try.</t>
+  </si>
+  <si>
+    <t>난 그거 시도해 볼 만한 가치가 있다고 말하는 거야.</t>
+  </si>
+  <si>
+    <t>All I'm saying is you guys should talk it out.</t>
+  </si>
+  <si>
+    <t>난 너희들이 대화로 문제를 해결하는 게 좋을 것 같다고 말하는 거야.</t>
+  </si>
+  <si>
+    <t>All I'm saying is you should consider his suggestion.</t>
+  </si>
+  <si>
+    <t>난 걔 제안을 고려해 보라고 말하는 것뿐이야.</t>
+  </si>
+  <si>
+    <t>All I'm saying is you should ask him yourself.</t>
+  </si>
+  <si>
+    <t>내 말은 네가 직접 걔한테 물어보라는 거야.</t>
+  </si>
+  <si>
+    <t>I have to say, you exceeded my expectations.</t>
+  </si>
+  <si>
+    <t>정말이지, 자넨 내 기대치를 넘어섰군.</t>
+  </si>
+  <si>
+    <t>I have to say, you really disappointed me.</t>
+  </si>
+  <si>
+    <t>정말이지, 넌 정말 날 실망시켰어.</t>
+  </si>
+  <si>
+    <t>I have to say, you made me feel so much better.</t>
+  </si>
+  <si>
+    <t>정말이지, 네 덕분에 기분이 한결 나아졌어.</t>
+  </si>
+  <si>
+    <t>I have to say, you look fantastic in that jacket.</t>
+  </si>
+  <si>
+    <t>정말이지, 너 그 재킷이 정말 잘 어울리는걸.</t>
+  </si>
+  <si>
+    <t>I have to say, I'm glad we tried this restaurant.</t>
+  </si>
+  <si>
+    <t>정말이지, 이 식당에 와 보길 잘했어.</t>
+  </si>
+  <si>
+    <t>Let's say he proposes to you tonight.</t>
+  </si>
+  <si>
+    <t>그 남자가 오늘 밤에 너한테 프러포즈한다고 치자.</t>
+  </si>
+  <si>
+    <t>Let's say you convince him to help us.</t>
+  </si>
+  <si>
+    <t>네가 걔한테 우리를 도와달라고 설득한다고 치자.</t>
+  </si>
+  <si>
+    <t>Let's say you just met the girl of your dreams.</t>
+  </si>
+  <si>
+    <t>네가 지금 막 이상형의 여자를 만났다고 치자.</t>
+  </si>
+  <si>
+    <t>Let's say he believes your excuse.</t>
+  </si>
+  <si>
+    <t>걔가 네 핑계를 믿어 준다고 치자.</t>
+  </si>
+  <si>
+    <t>Let's say I know something about it. I'm not going to tell you.</t>
+  </si>
+  <si>
+    <t>내가 그것에 대해 뭔가를 안다고 치자. 하지만 난 너한테 아무 말도 안 할 거야.</t>
+  </si>
+  <si>
+    <t>Let's just say he won't be hearing from me again.</t>
+  </si>
+  <si>
+    <t>걔가 다시는 나한테 연락 받을 일은 없을 거라고만 말해 두지.</t>
+  </si>
+  <si>
+    <t>Let's just say you don't want to know.</t>
+  </si>
+  <si>
+    <t>넌 알고 싶지 않을 거라고만 말해 둘게.</t>
+  </si>
+  <si>
+    <t>Let's just say I don't want to see her again.</t>
+  </si>
+  <si>
+    <t>그 여자 다시 보고 싶지 않다고만 말해 둘게.</t>
+  </si>
+  <si>
+    <t>Let's just say she and I have differences in opinion.</t>
+  </si>
+  <si>
+    <t>걔하고 나하고 의견 차이가 있다고만 말할게.</t>
+  </si>
+  <si>
+    <t>Let's just say I had a wonderful time.</t>
+  </si>
+  <si>
+    <t>정말 즐거운 시간을 보냈다고만 말해 둘게.</t>
+  </si>
+  <si>
+    <t>It's like saying you're better than everyone else.</t>
+  </si>
+  <si>
+    <t>그건 네가 다른 사람들보다 낫다고 말하는 거나 마찬가지야.</t>
+  </si>
+  <si>
+    <t>That's like saying you won when you really lost.</t>
+  </si>
+  <si>
+    <t>그건 네가 사실은 져놓고 이겼다고 말하는 거나 마찬가지야.</t>
+  </si>
+  <si>
+    <t>It's like saying it's all my responsibility.</t>
+  </si>
+  <si>
+    <t>그건 그게 전부 내 책임이라고 말하는 거나 마찬가지잖아.</t>
+  </si>
+  <si>
+    <t>That's like saying it's okay to cheat on exams.</t>
+  </si>
+  <si>
+    <t>그건 시험에서 커닝해도 괜찮다고 말하는 거나 마찬가지야.</t>
+  </si>
+  <si>
+    <t>He's a little weird, to say the least.</t>
+  </si>
+  <si>
+    <t>걘 좀 이상해, 아무리 좋게 봐도 말이야.</t>
+  </si>
+  <si>
+    <t>I wasn't happy with the results, to say the least.</t>
+  </si>
+  <si>
+    <t>결과가 만족스럽지 않았어, 아무리 좋게 봐도 말이야.</t>
+  </si>
+  <si>
+    <t>The news was really upsetting, to say the least.</t>
+  </si>
+  <si>
+    <t>그 소식 때문에 정말 속상했어, 과장하지 않고 말이야.</t>
+  </si>
+  <si>
+    <t>The service was horrible, to say the least.</t>
+  </si>
+  <si>
+    <t>서비스가 형편없었어, 과장하지 않고 말이야.</t>
+  </si>
+  <si>
+    <t>Yeah, I'm mad at you, to say the least.</t>
+  </si>
+  <si>
+    <t>그래, 나 너한테 화났어, 과장하지 않고 말이야.</t>
+  </si>
+  <si>
+    <t>You always talk about how you're so special.</t>
+  </si>
+  <si>
+    <t>넌 항상 네가 특별하다고 말하더라. (넌 항상 네가 무슨 대단한 사람인 것처럼 말하더라)</t>
+  </si>
+  <si>
+    <t>He always talks about how he's so good with women.</t>
+  </si>
+  <si>
+    <t>걘 항상 자기가 여자를 잘 다룬다고 하더라. (걘 툭 하면 자기가 여자한테 인기 많다고 말하더라고)</t>
+  </si>
+  <si>
+    <t>Jane talked about how she is done with men.</t>
+  </si>
+  <si>
+    <t>제인은 자기가 남자들하고는 끝이라고 얘기하더라.</t>
+  </si>
+  <si>
+    <t>Please tell me that you believe me.</t>
+  </si>
+  <si>
+    <t>내 말을 믿는다고 말해 줘.</t>
+  </si>
+  <si>
+    <t>Please tell me he said yes.</t>
+  </si>
+  <si>
+    <t>제발 걔가 승낙했다고 말해 줘.</t>
+  </si>
+  <si>
+    <t>Please tell me I didn't come all the way here for nothing.</t>
+  </si>
+  <si>
+    <t>내가 아무것도 아닌 것 갖고 (허사로) 이 먼 길을 온 게 아니라고 말해 줘.</t>
+  </si>
+  <si>
+    <t>Please tell me you didn't tell anyone my secret.</t>
+  </si>
+  <si>
+    <t>제발 내 비밀을 아무한테도 말 안 했다고 말해 줘.</t>
+  </si>
+  <si>
+    <t>Don't tell me that you don't remember.</t>
+  </si>
+  <si>
+    <t>설마 기억 안 난다는 건 아니겠지?</t>
+  </si>
+  <si>
+    <t>Don't tell me you changed your mind again.</t>
+  </si>
+  <si>
+    <t>설마 또 마음을 바꿨다는 건 아니겠지?</t>
+  </si>
+  <si>
+    <t>Don't tell me you forgot to ask him about it.</t>
+  </si>
+  <si>
+    <t>설마 걔한테 그것에 대해서 묻는 거 까먹었다는 건 아니겠지?</t>
+  </si>
+  <si>
+    <t>Don't tell me you bombed the math test.</t>
+  </si>
+  <si>
+    <t>설마 수학 시험을 망쳤다는 건 아니겠지?</t>
+  </si>
+  <si>
+    <t>Don't tell me you've been dozing off the whole time.</t>
+  </si>
+  <si>
+    <t>설마 여태까지 내내 졸고 있었던 건 아니겠지?</t>
+  </si>
+  <si>
+    <t>Ryan tells me you've got a new girlfriend.</t>
+  </si>
+  <si>
+    <t>라이언이 너 새 여자 친구 생겼다고 말하더라.</t>
+  </si>
+  <si>
+    <t>Sally tells me that you're up for a promotion.</t>
+  </si>
+  <si>
+    <t>샐리가 너 승진 대상자라고 말하더라.</t>
+  </si>
+  <si>
+    <t>Emma tells me that you're expecting.</t>
+  </si>
+  <si>
+    <t>엠마가 너 임신했다고 말하더라.</t>
+  </si>
+  <si>
+    <t>Aiden tells me you're considering leaving the company.</t>
+  </si>
+  <si>
+    <t>에이든이 너 회사 그만두는 걸 고려 중이라고 말하더라.</t>
+  </si>
+  <si>
+    <t>I'm telling you, I'm right!</t>
+  </si>
+  <si>
+    <t>진짜라니까! 내 말이 맞다니까!</t>
+  </si>
+  <si>
+    <t>I'm telling you, he's lying.</t>
+  </si>
+  <si>
+    <t>진짜라니까! 걔 거짓말하는 거야.</t>
+  </si>
+  <si>
+    <t>I'm telling you, this is better than that one.</t>
+  </si>
+  <si>
+    <t>진짜라니까! 이게 저것보다 낫다니까.</t>
+  </si>
+  <si>
+    <t>I'm telling you, I've never seen anything like it in my life!</t>
+  </si>
+  <si>
+    <t>진짜라니까! 내 평생 그런 거 본 적 없다니까!</t>
+  </si>
+  <si>
+    <t>I'll tell you what, we'll go together.</t>
+  </si>
+  <si>
+    <t>이건 어때, 우리 같이 가는 거야.</t>
+  </si>
+  <si>
+    <t>I'll tell you what, we'll try it your way and see what happens.</t>
+  </si>
+  <si>
+    <t>이건 어때, 네 방법대로 해 보고 어떻게 되나 한번 보자.</t>
+  </si>
+  <si>
+    <t>I'll tell you what, I'll let you borrow my car if you promise to return it tomorrow.</t>
+  </si>
+  <si>
+    <t>이건 어때, 네가 내일 돌려준다고 약속하면 차 빌려 줄게.</t>
+  </si>
+  <si>
+    <t>I can tell what you're thinking.</t>
+  </si>
+  <si>
+    <t>난 네가 무슨 생각을 하고 있는지 알 수 있어.</t>
+  </si>
+  <si>
+    <t>I can always tell when you're feeling down.</t>
+  </si>
+  <si>
+    <t>난 네가 기분이 우울하면 항상 알 수 있어.</t>
+  </si>
+  <si>
+    <t>I can tell that you want to say something to me.</t>
+  </si>
+  <si>
+    <t>난 네가 나한테 뭔가 말하고 싶어한다는 것을 알 수 있어. (너 나한테 할 말이 있구나)</t>
+  </si>
+  <si>
+    <t>I can tell that you're thinking about me.</t>
+  </si>
+  <si>
+    <t>난 네가 내 생각 하고 있다는 것을 알 수 있어.</t>
+  </si>
+  <si>
+    <t>I can tell there's something you're not telling me.</t>
+  </si>
+  <si>
+    <t>난 네가 나한테 말 안 하고 있는 뭔가가 있다는 것을 알 수 있어.</t>
+  </si>
+  <si>
+    <t>You can never tell how John will react.</t>
+  </si>
+  <si>
+    <t>존이 어떤 반응을 보일지 도무지 알 수 없어.</t>
+  </si>
+  <si>
+    <t>You can never tell if Lily is angry or not.</t>
+  </si>
+  <si>
+    <t>릴리가 화난 건지 아닌지 도무지 알 수 없다니까.</t>
+  </si>
+  <si>
+    <t>You can never tell what she's thinking.</t>
+  </si>
+  <si>
+    <t>걔가 무슨 생각을 하고 있는지 도무지 알 수 없어.</t>
+  </si>
+  <si>
+    <t>You can never tell when Grace is going to throw a tantrum.</t>
+  </si>
+  <si>
+    <t>그레이스가 언제 짜증 부릴지 도무지 알 수 없어.</t>
+  </si>
+  <si>
+    <t>I'm good with numbers.</t>
+  </si>
+  <si>
+    <t>난 숫자에 밝아.</t>
+  </si>
+  <si>
+    <t>I'm not good with words.</t>
+  </si>
+  <si>
+    <t>난 말주변이 없어.</t>
+  </si>
+  <si>
+    <t>I'm good with computers.</t>
+  </si>
+  <si>
+    <t>난 컴퓨터를 잘 다뤄.</t>
+  </si>
+  <si>
+    <t>I'm good with my hands.</t>
+  </si>
+  <si>
+    <t>난 손을 잘 다뤄. (손재주가 좋아)</t>
+  </si>
+  <si>
+    <t>I'm good with people.</t>
+  </si>
+  <si>
+    <t>난 사람들을 잘 다뤄. (사람들하고 잘 어울려)</t>
+  </si>
+  <si>
+    <t>I'm not cut out to be a doctor.</t>
+  </si>
+  <si>
+    <t>난 의사가 될 소질이 없어.</t>
+  </si>
+  <si>
+    <t>I'm not cut out for long-term relationships.</t>
+  </si>
+  <si>
+    <t>(한 사람하고) 오랫동안 연애하는 건 나한테 안 맞아.</t>
+  </si>
+  <si>
+    <t>I'm not cut out for public speaking.</t>
+  </si>
+  <si>
+    <t>난 대중 연설에 소질이 없어.</t>
+  </si>
+  <si>
+    <t>I'm not cut out to be a mother.</t>
+  </si>
+  <si>
+    <t>난 엄마가 될 소질이 없어. (엄마가 될 자신이 없어)</t>
   </si>
 </sst>
 </file>
@@ -295,8 +867,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="33.63"/>
-    <col customWidth="1" min="3" max="3" width="31.75"/>
+    <col customWidth="1" min="2" max="2" width="41.88"/>
+    <col customWidth="1" min="3" max="3" width="60.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -334,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -343,7 +915,1053 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="$A$1:$C$99"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>